--- a/Documento/pia.xlsx
+++ b/Documento/pia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soporte\Desktop\PiaDiseno\PiaDiseno\Documento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0B0C36-5E9C-40FB-AFCE-AA442D6DFFF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416D5A9E-9531-493F-90B1-C2387A9082ED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9949CDD4-C413-4234-AC28-623D5436FA5B}"/>
   </bookViews>
@@ -805,7 +805,7 @@
     <col min="5" max="5" width="13.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" customWidth="1"/>
     <col min="15" max="15" width="2.85546875" customWidth="1"/>
     <col min="21" max="21" width="39.85546875" customWidth="1"/>
   </cols>
